--- a/reports/二级子公司C_利润表_2025-04.xlsx
+++ b/reports/二级子公司C_利润表_2025-04.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>88604577</v>
+        <v>89690247</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>86068462</v>
+        <v>85119810</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>322485618</v>
+        <v>321548754</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>397604</v>
+        <v>402225</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1502305</v>
+        <v>1503935</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>348039</v>
+        <v>352098</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1312784</v>
+        <v>1317909</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>298731</v>
+        <v>301612</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1124242</v>
+        <v>1131033</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>279408</v>
+        <v>281066</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1048976</v>
+        <v>1056437</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>150056</v>
+        <v>150236</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>562141</v>
+        <v>566037</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>120336</v>
+        <v>119887</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>450128</v>
+        <v>452614</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>87010403</v>
+        <v>88083123</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>84474288</v>
+        <v>83512686</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>80472055</v>
+        <v>79525041</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>301375658</v>
+        <v>300553456</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1205923</v>
+        <v>1193076</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>4525589</v>
+        <v>4502078</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>802482</v>
+        <v>796329</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>3018769</v>
+        <v>2998398</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3002167</v>
+        <v>2992204</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>11319684</v>
+        <v>11239139</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>399286</v>
+        <v>399939</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>1508266</v>
+        <v>1498862</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>298807</v>
+        <v>300696</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1129870</v>
+        <v>1125057</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>497265</v>
+        <v>502193</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>1880348</v>
+        <v>1877478</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>596400</v>
+        <v>603408</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>2253023</v>
+        <v>2256364</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2486314</v>
+        <v>2514933</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>9375640</v>
+        <v>9415373</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>49801</v>
+        <v>50261</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>199341</v>
+        <v>200529</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1204249</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>4527847</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>800994</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>3018780</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>60065208</v>
+        <v>63788731</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>53513719</v>
+        <v>52920751</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>52306723</v>
+        <v>51727923</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>195653073</v>
+        <v>195618264</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1206996</v>
+        <v>1192828</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>4521404</v>
+        <v>4507409</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1988662</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>7502266</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>637207</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>2398497</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>399084</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1498537</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>480089</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>1798770</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>360946</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1350267</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>241106</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>901362</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>201156</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>752275</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>895205</v>
+        <v>905339</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>3374760</v>
+        <v>3390143</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>697391</v>
+        <v>703529</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>2622859</v>
+        <v>2639755</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>599118</v>
+        <v>601958</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>2247869</v>
+        <v>2264029</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4504701</v>
+        <v>4504095</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>16867523</v>
+        <v>16979979</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>200675</v>
+        <v>199680</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>798194</v>
+        <v>754187</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>351790</v>
+        <v>348658</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1398745</v>
+        <v>1402768</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>402380</v>
+        <v>348658</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1600995</v>
+        <v>1402768</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>50287</v>
+        <v>49700</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>200406</v>
+        <v>199808</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>179001</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>718338</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>348556</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1311570</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>119763</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>478262</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>90047</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>358792</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>150439</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>598501</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>502409</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>1878207</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>80469</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>320099</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>60352</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>240422</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>100485</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>401162</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>70208</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>280991</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>50029</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>200710</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>39923</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>160469</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>29877</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>120217</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>26945195</v>
+        <v>25525770</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>31519975</v>
+        <v>28828488</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>198918</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>750005</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>49806</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>199332</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>79977</v>
+        <v>79868</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>321090</v>
+        <v>318841</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>26865218</v>
+        <v>25644820</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2786910</v>
+        <v>2809010</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>11214935</v>
+        <v>11173728</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>24078308</v>
+        <v>22835810</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>24078308</v>
+        <v>22835810</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>24078308</v>
+        <v>22835810</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>24078308</v>
+        <v>22835810</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>24078308</v>
+        <v>22835810</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
